--- a/research/traditional_assets/database/data/south_korea/south_korea_insurance_prop_cas.xlsx
+++ b/research/traditional_assets/database/data/south_korea/south_korea_insurance_prop_cas.xlsx
@@ -588,121 +588,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0405</v>
+        <v>0.0371</v>
       </c>
       <c r="E2">
-        <v>0.0698</v>
+        <v>0.0481</v>
       </c>
       <c r="G2">
-        <v>0.06712467276187452</v>
+        <v>0.05834058827468745</v>
       </c>
       <c r="H2">
-        <v>0.06712467276187452</v>
+        <v>0.05834058827468745</v>
       </c>
       <c r="I2">
-        <v>0.05860655362123161</v>
+        <v>0.01075118959921954</v>
       </c>
       <c r="J2">
-        <v>0.04503871914126206</v>
+        <v>0.007936493051489347</v>
       </c>
       <c r="K2">
-        <v>2668.98</v>
+        <v>2776.2</v>
       </c>
       <c r="L2">
-        <v>0.04076508808318646</v>
+        <v>0.05024823664200892</v>
       </c>
       <c r="M2">
-        <v>760.6724</v>
+        <v>816.4536000000001</v>
       </c>
       <c r="N2">
-        <v>0.0484322706753513</v>
+        <v>0.04937431059506531</v>
       </c>
       <c r="O2">
-        <v>0.2850049082421</v>
+        <v>0.2940903393127296</v>
       </c>
       <c r="P2">
-        <v>620.9384</v>
+        <v>630.0536</v>
       </c>
       <c r="Q2">
-        <v>0.0395353593235663</v>
+        <v>0.03810193517174649</v>
       </c>
       <c r="R2">
-        <v>0.2326500760590188</v>
+        <v>0.2269482025790649</v>
       </c>
       <c r="S2">
-        <v>139.734</v>
+        <v>186.4</v>
       </c>
       <c r="T2">
-        <v>0.1836980019256647</v>
+        <v>0.2283044621274253</v>
       </c>
       <c r="U2">
-        <v>0.07200000000000001</v>
+        <v>0.021</v>
       </c>
       <c r="V2">
-        <v>4.584264512062347e-06</v>
+        <v>1.269956458635704e-06</v>
       </c>
       <c r="W2">
-        <v>0.0758465288103377</v>
+        <v>0.1038666249217282</v>
       </c>
       <c r="X2">
-        <v>0.07186597149182337</v>
+        <v>0.1035081850071165</v>
       </c>
       <c r="Y2">
-        <v>0.003980557318514322</v>
+        <v>0.0003584399146117218</v>
       </c>
       <c r="Z2">
-        <v>2.008992570874213</v>
+        <v>1.710431876951761</v>
       </c>
       <c r="AA2">
-        <v>0.07731462782668555</v>
+        <v>0.01507212103651948</v>
       </c>
       <c r="AB2">
-        <v>0.0511401214805116</v>
+        <v>0.08301392859694183</v>
       </c>
       <c r="AC2">
-        <v>0.02545871143395877</v>
+        <v>-0.06722168882782818</v>
       </c>
       <c r="AD2">
-        <v>4782.2</v>
+        <v>4395.4</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>4782.2</v>
+        <v>4395.4</v>
       </c>
       <c r="AG2">
-        <v>4782.128</v>
+        <v>4395.379</v>
       </c>
       <c r="AH2">
-        <v>0.2334135424953998</v>
+        <v>0.2099907316280803</v>
       </c>
       <c r="AI2">
-        <v>0.1473372872217515</v>
+        <v>0.2242207825332857</v>
       </c>
       <c r="AJ2">
-        <v>0.2334108485209021</v>
+        <v>0.2099899390288619</v>
       </c>
       <c r="AK2">
-        <v>0.147335395768266</v>
+        <v>0.2242199514675805</v>
       </c>
       <c r="AL2">
-        <v>232.2</v>
+        <v>253</v>
       </c>
       <c r="AM2">
-        <v>232.2</v>
+        <v>253</v>
       </c>
       <c r="AN2">
-        <v>1.079503386004515</v>
+        <v>3.989290252314394</v>
       </c>
       <c r="AO2">
-        <v>16.52497846683893</v>
+        <v>2.347826086956522</v>
       </c>
       <c r="AP2">
-        <v>1.079487133182844</v>
+        <v>3.989271192593937</v>
       </c>
       <c r="AQ2">
-        <v>16.52497846683893</v>
+        <v>2.347826086956522</v>
       </c>
     </row>
     <row r="3">
@@ -722,121 +722,121 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.09320000000000001</v>
+        <v>0.101</v>
       </c>
       <c r="E3">
-        <v>0.207</v>
+        <v>0.208</v>
       </c>
       <c r="G3">
-        <v>0.06257746155611658</v>
+        <v>0.0977416440831075</v>
       </c>
       <c r="H3">
-        <v>0.06257746155611658</v>
+        <v>0.0977416440831075</v>
       </c>
       <c r="I3">
-        <v>0.08360110167546476</v>
+        <v>0.09607691315008388</v>
       </c>
       <c r="J3">
-        <v>0.06093043576867496</v>
+        <v>0.06974116494706759</v>
       </c>
       <c r="K3">
-        <v>503.7</v>
+        <v>638.2</v>
       </c>
       <c r="L3">
-        <v>0.05780353454211613</v>
+        <v>0.08235901406633114</v>
       </c>
       <c r="M3">
-        <v>245.812</v>
+        <v>233.4016</v>
       </c>
       <c r="N3">
-        <v>0.07495868020614155</v>
+        <v>0.05454327911759208</v>
       </c>
       <c r="O3">
-        <v>0.4880127059757793</v>
+        <v>0.3657185835161391</v>
       </c>
       <c r="P3">
-        <v>125.712</v>
+        <v>47.0016</v>
       </c>
       <c r="Q3">
-        <v>0.03833501052053792</v>
+        <v>0.01098373527762199</v>
       </c>
       <c r="R3">
-        <v>0.2495771292435974</v>
+        <v>0.0736471325603259</v>
       </c>
       <c r="S3">
-        <v>120.1</v>
+        <v>186.4</v>
       </c>
       <c r="T3">
-        <v>0.488584772102257</v>
+        <v>0.7986234884422386</v>
       </c>
       <c r="U3">
         <v>0.003</v>
       </c>
       <c r="V3">
-        <v>9.148293843198243e-07</v>
+        <v>7.010656197420079e-07</v>
       </c>
       <c r="W3">
-        <v>0.2150358606557377</v>
+        <v>0.3116363103667171</v>
       </c>
       <c r="X3">
-        <v>0.05866673961598798</v>
+        <v>0.09335633705675071</v>
       </c>
       <c r="Y3">
-        <v>0.1563691210397497</v>
+        <v>0.2182799733099664</v>
       </c>
       <c r="Z3">
-        <v>2.919559338854162</v>
+        <v>2.711244579872552</v>
       </c>
       <c r="AA3">
-        <v>0.1778900227688887</v>
+        <v>0.1890853554567346</v>
       </c>
       <c r="AB3">
-        <v>0.0511401214805116</v>
+        <v>0.08482353275249765</v>
       </c>
       <c r="AC3">
-        <v>0.126749901288377</v>
+        <v>0.1042618227042369</v>
       </c>
       <c r="AD3">
-        <v>810.2</v>
+        <v>935.2</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>810.2</v>
+        <v>935.2</v>
       </c>
       <c r="AG3">
-        <v>810.197</v>
+        <v>935.197</v>
       </c>
       <c r="AH3">
-        <v>0.1981171292334026</v>
+        <v>0.1793494937097269</v>
       </c>
       <c r="AI3">
-        <v>0.2826739236619915</v>
+        <v>0.6848271821909784</v>
       </c>
       <c r="AJ3">
-        <v>0.198116540982913</v>
+        <v>0.1793490215647179</v>
       </c>
       <c r="AK3">
-        <v>0.2826731728489005</v>
+        <v>0.6848264898062899</v>
       </c>
       <c r="AL3">
-        <v>29.3</v>
+        <v>34.8</v>
       </c>
       <c r="AM3">
-        <v>29.3</v>
+        <v>34.8</v>
       </c>
       <c r="AN3">
-        <v>1.044341325083785</v>
+        <v>1.189973279043135</v>
       </c>
       <c r="AO3">
-        <v>24.86348122866894</v>
+        <v>21.39367816091954</v>
       </c>
       <c r="AP3">
-        <v>1.04433745810776</v>
+        <v>1.189969461763583</v>
       </c>
       <c r="AQ3">
-        <v>24.86348122866894</v>
+        <v>21.39367816091954</v>
       </c>
     </row>
     <row r="4">
@@ -856,28 +856,28 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0277</v>
+        <v>-0.0125</v>
       </c>
       <c r="E4">
-        <v>0.0526</v>
+        <v>0.00444</v>
       </c>
       <c r="G4">
-        <v>0.09051280795415585</v>
+        <v>0.06924355265587492</v>
       </c>
       <c r="H4">
-        <v>0.09051280795415585</v>
+        <v>0.06924355265587492</v>
       </c>
       <c r="I4">
-        <v>0.07963951608953322</v>
+        <v>0.04462362282267495</v>
       </c>
       <c r="J4">
-        <v>0.07963951608953322</v>
+        <v>0.03413936489076894</v>
       </c>
       <c r="K4">
-        <v>8.68</v>
+        <v>52.1</v>
       </c>
       <c r="L4">
-        <v>0.004251359161483077</v>
+        <v>0.03206745860774297</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -907,67 +907,67 @@
         <v>0</v>
       </c>
       <c r="W4">
-        <v>0.009565792373815296</v>
+        <v>0.0586381541924592</v>
       </c>
       <c r="X4">
-        <v>0.07331434547079158</v>
+        <v>0.1180545949926688</v>
       </c>
       <c r="Y4">
-        <v>-0.06374855309697627</v>
+        <v>-0.05941644080020958</v>
       </c>
       <c r="Z4">
-        <v>1.602590266875981</v>
+        <v>1.336211859527922</v>
       </c>
       <c r="AA4">
-        <v>0.127629513343799</v>
+        <v>0.04561742424379661</v>
       </c>
       <c r="AB4">
-        <v>0.05027450938836062</v>
+        <v>0.0806325582045499</v>
       </c>
       <c r="AC4">
-        <v>0.07735500395543843</v>
+        <v>-0.03501513396075329</v>
       </c>
       <c r="AD4">
-        <v>327.4</v>
+        <v>318.7</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>327.4</v>
+        <v>318.7</v>
       </c>
       <c r="AG4">
-        <v>327.4</v>
+        <v>318.7</v>
       </c>
       <c r="AH4">
-        <v>0.4377005347593583</v>
+        <v>0.4794644200391153</v>
       </c>
       <c r="AI4">
-        <v>0.2692655646023521</v>
+        <v>0.4287636216870712</v>
       </c>
       <c r="AJ4">
-        <v>0.4377005347593583</v>
+        <v>0.4794644200391153</v>
       </c>
       <c r="AK4">
-        <v>0.2692655646023521</v>
+        <v>0.4287636216870712</v>
       </c>
       <c r="AL4">
-        <v>17.7</v>
+        <v>14.1</v>
       </c>
       <c r="AM4">
-        <v>17.7</v>
+        <v>14.1</v>
       </c>
       <c r="AN4">
-        <v>1.797913234486546</v>
+        <v>3.521546961325967</v>
       </c>
       <c r="AO4">
-        <v>9.186440677966102</v>
+        <v>5.141843971631205</v>
       </c>
       <c r="AP4">
-        <v>1.797913234486546</v>
+        <v>3.521546961325967</v>
       </c>
       <c r="AQ4">
-        <v>9.186440677966102</v>
+        <v>5.141843971631205</v>
       </c>
     </row>
     <row r="5">
@@ -978,7 +978,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>DB Insurance Co., Ltd. (KOSE:A005830)</t>
+          <t>Samsung Fire &amp; Marine Insurance Co., Ltd. (KOSE:A000810)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -987,46 +987,46 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.0405</v>
+        <v>0.0166</v>
       </c>
       <c r="E5">
-        <v>0.112</v>
+        <v>0.008529999999999999</v>
       </c>
       <c r="G5">
-        <v>0.07964953945890434</v>
+        <v>0.08804562204806145</v>
       </c>
       <c r="H5">
-        <v>0.07964953945890434</v>
+        <v>0.08804562204806145</v>
       </c>
       <c r="I5">
-        <v>0.05405821752944575</v>
+        <v>0.0369349146208543</v>
       </c>
       <c r="J5">
-        <v>0.03978445151873694</v>
+        <v>0.0271572179329883</v>
       </c>
       <c r="K5">
-        <v>674.4</v>
+        <v>806.1</v>
       </c>
       <c r="L5">
-        <v>0.04328765364742129</v>
+        <v>0.05229797062334562</v>
       </c>
       <c r="M5">
-        <v>111.6</v>
+        <v>355.9</v>
       </c>
       <c r="N5">
-        <v>0.04097517990894405</v>
+        <v>0.05576971292465838</v>
       </c>
       <c r="O5">
-        <v>0.1654804270462634</v>
+        <v>0.4415084977049993</v>
       </c>
       <c r="P5">
-        <v>111.6</v>
+        <v>355.9</v>
       </c>
       <c r="Q5">
-        <v>0.04097517990894405</v>
+        <v>0.05576971292465838</v>
       </c>
       <c r="R5">
-        <v>0.1654804270462634</v>
+        <v>0.4415084977049993</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -1035,73 +1035,73 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>0.017</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>2.663908737620659e-06</v>
       </c>
       <c r="W5">
-        <v>0.1191772107160529</v>
+        <v>0.06229617150187793</v>
       </c>
       <c r="X5">
-        <v>0.07024163441135695</v>
+        <v>0.08567336415958873</v>
       </c>
       <c r="Y5">
-        <v>0.04893557630469592</v>
+        <v>-0.0233771926577108</v>
       </c>
       <c r="Z5">
-        <v>2.209419406075389</v>
+        <v>1.19118386686834</v>
       </c>
       <c r="AA5">
-        <v>0.08790053924556288</v>
+        <v>0.03234923987080324</v>
       </c>
       <c r="AB5">
-        <v>0.05041035492172988</v>
+        <v>0.08567336415958873</v>
       </c>
       <c r="AC5">
-        <v>0.037490184323833</v>
+        <v>-0.0533241242887855</v>
       </c>
       <c r="AD5">
-        <v>1816.5</v>
+        <v>0</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>1816.5</v>
+        <v>0</v>
       </c>
       <c r="AG5">
-        <v>1816.5</v>
+        <v>-0.017</v>
       </c>
       <c r="AH5">
-        <v>0.4001013193541992</v>
+        <v>0</v>
       </c>
       <c r="AI5">
-        <v>0.2447816302604806</v>
+        <v>0</v>
       </c>
       <c r="AJ5">
-        <v>0.4001013193541992</v>
+        <v>-2.663915834049326e-06</v>
       </c>
       <c r="AK5">
-        <v>0.2447816302604806</v>
+        <v>-2.348104244226047e-06</v>
       </c>
       <c r="AL5">
-        <v>61.1</v>
+        <v>52.1</v>
       </c>
       <c r="AM5">
-        <v>61.1</v>
+        <v>52.1</v>
       </c>
       <c r="AN5">
-        <v>1.924666242848061</v>
+        <v>0</v>
       </c>
       <c r="AO5">
-        <v>13.78396072013093</v>
+        <v>10.92706333973129</v>
       </c>
       <c r="AP5">
-        <v>1.924666242848061</v>
+        <v>-2.179207793872581e-05</v>
       </c>
       <c r="AQ5">
-        <v>13.78396072013093</v>
+        <v>10.92706333973129</v>
       </c>
     </row>
     <row r="6">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Samsung Fire &amp; Marine Insurance Co., Ltd. (KOSE:A000810)</t>
+          <t>Hanwha General Insurance Co., Ltd. (KOSE:A000370)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1121,121 +1121,118 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.022</v>
+        <v>0.0371</v>
       </c>
       <c r="E6">
-        <v>0.0698</v>
+        <v>0.0481</v>
       </c>
       <c r="G6">
-        <v>0.07967644959664338</v>
+        <v>0.03055464967513735</v>
       </c>
       <c r="H6">
-        <v>0.07967644959664338</v>
+        <v>0.03055464967513735</v>
       </c>
       <c r="I6">
-        <v>0.07382074961610831</v>
+        <v>0.009081102777011263</v>
       </c>
       <c r="J6">
-        <v>0.05454226193567403</v>
+        <v>0.006364145731297087</v>
       </c>
       <c r="K6">
-        <v>989.6</v>
+        <v>132.7</v>
       </c>
       <c r="L6">
-        <v>0.0535069316780933</v>
+        <v>0.03328901487595012</v>
       </c>
       <c r="M6">
-        <v>317.3</v>
+        <v>-0</v>
       </c>
       <c r="N6">
-        <v>0.04399001802301401</v>
+        <v>-0</v>
       </c>
       <c r="O6">
-        <v>0.3206345998383185</v>
+        <v>-0</v>
       </c>
       <c r="P6">
-        <v>317.3</v>
+        <v>-0</v>
       </c>
       <c r="Q6">
-        <v>0.04399001802301401</v>
+        <v>-0</v>
       </c>
       <c r="R6">
-        <v>0.3206345998383185</v>
+        <v>-0</v>
       </c>
       <c r="S6">
         <v>0</v>
       </c>
-      <c r="T6">
-        <v>0</v>
-      </c>
       <c r="U6">
-        <v>0.068</v>
+        <v>0</v>
       </c>
       <c r="V6">
-        <v>9.427422708997643e-06</v>
+        <v>0</v>
       </c>
       <c r="W6">
-        <v>0.0758465288103377</v>
+        <v>0.1038666249217282</v>
       </c>
       <c r="X6">
-        <v>0.05185591639272678</v>
+        <v>0.127231360785379</v>
       </c>
       <c r="Y6">
-        <v>0.02399061241761091</v>
+        <v>-0.02336473586365079</v>
       </c>
       <c r="Z6">
-        <v>1.417517812478492</v>
+        <v>2.368286596958175</v>
       </c>
       <c r="AA6">
-        <v>0.07731462782668555</v>
+        <v>0.01507212103651948</v>
       </c>
       <c r="AB6">
-        <v>0.05185591639272678</v>
+        <v>0.08229380986434766</v>
       </c>
       <c r="AC6">
-        <v>0.02545871143395877</v>
+        <v>-0.06722168882782818</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>508.2</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>508.2</v>
       </c>
       <c r="AG6">
-        <v>-0.068</v>
+        <v>508.2</v>
       </c>
       <c r="AH6">
-        <v>0</v>
+        <v>0.5417332906939559</v>
       </c>
       <c r="AI6">
-        <v>0</v>
+        <v>0.8145536143612758</v>
       </c>
       <c r="AJ6">
-        <v>-9.427511586134461e-06</v>
+        <v>0.5417332906939559</v>
       </c>
       <c r="AK6">
-        <v>-5.246576762973242e-06</v>
+        <v>0.8145536143612758</v>
       </c>
       <c r="AL6">
-        <v>45.3</v>
+        <v>20.7</v>
       </c>
       <c r="AM6">
-        <v>45.3</v>
+        <v>20.7</v>
       </c>
       <c r="AN6">
-        <v>0</v>
+        <v>5.888760139049826</v>
       </c>
       <c r="AO6">
-        <v>30.13907284768212</v>
+        <v>1.748792270531401</v>
       </c>
       <c r="AP6">
-        <v>-4.201680672268908e-05</v>
+        <v>5.888760139049826</v>
       </c>
       <c r="AQ6">
-        <v>30.13907284768212</v>
+        <v>1.748792270531401</v>
       </c>
     </row>
     <row r="7">
@@ -1255,52 +1252,52 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.0415</v>
+        <v>0.0451</v>
       </c>
       <c r="E7">
-        <v>0.0362</v>
+        <v>0.036</v>
       </c>
       <c r="G7">
-        <v>0.04539633803871645</v>
+        <v>0.030175806874836</v>
       </c>
       <c r="H7">
-        <v>0.04539633803871645</v>
+        <v>0.030175806874836</v>
       </c>
       <c r="I7">
-        <v>0.03696409181113566</v>
+        <v>-0.02201521910259774</v>
       </c>
       <c r="J7">
-        <v>0.0260364866835887</v>
+        <v>-0.01596282387580743</v>
       </c>
       <c r="K7">
-        <v>323.8</v>
+        <v>379</v>
       </c>
       <c r="L7">
-        <v>0.02424832440933089</v>
+        <v>0.03314965450887781</v>
       </c>
       <c r="M7">
-        <v>85.52640000000001</v>
+        <v>80.75200000000001</v>
       </c>
       <c r="N7">
-        <v>0.0565763048223854</v>
+        <v>0.04420649258225216</v>
       </c>
       <c r="O7">
-        <v>0.2641334156886967</v>
+        <v>0.213065963060686</v>
       </c>
       <c r="P7">
-        <v>66.32640000000001</v>
+        <v>80.75200000000001</v>
       </c>
       <c r="Q7">
-        <v>0.04387537209763842</v>
+        <v>0.04420649258225216</v>
       </c>
       <c r="R7">
-        <v>0.2048375540457072</v>
+        <v>0.213065963060686</v>
       </c>
       <c r="S7">
-        <v>19.2</v>
+        <v>0</v>
       </c>
       <c r="T7">
-        <v>0.2244920866539455</v>
+        <v>0</v>
       </c>
       <c r="U7">
         <v>0</v>
@@ -1309,67 +1306,67 @@
         <v>0</v>
       </c>
       <c r="W7">
-        <v>0.07516423315304442</v>
+        <v>0.0894606396789803</v>
       </c>
       <c r="X7">
-        <v>0.07186597149182337</v>
+        <v>0.1018565682660915</v>
       </c>
       <c r="Y7">
-        <v>0.003298261661221047</v>
+        <v>-0.01239592858711121</v>
       </c>
       <c r="Z7">
-        <v>2.566302802014068</v>
+        <v>2.143499943754922</v>
       </c>
       <c r="AA7">
-        <v>0.06681750873069565</v>
+        <v>-0.03421631207996294</v>
       </c>
       <c r="AB7">
-        <v>0.0503363562947266</v>
+        <v>0.08507808606671824</v>
       </c>
       <c r="AC7">
-        <v>0.01648115243596905</v>
+        <v>-0.1192943981466812</v>
       </c>
       <c r="AD7">
-        <v>1097.3</v>
+        <v>840.9</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>1097.3</v>
+        <v>840.9</v>
       </c>
       <c r="AG7">
-        <v>1097.3</v>
+        <v>840.9</v>
       </c>
       <c r="AH7">
-        <v>0.4205825986968187</v>
+        <v>0.3152271704903284</v>
       </c>
       <c r="AI7">
-        <v>0.2057257489969627</v>
+        <v>0.224347686889707</v>
       </c>
       <c r="AJ7">
-        <v>0.4205825986968187</v>
+        <v>0.3152271704903284</v>
       </c>
       <c r="AK7">
-        <v>0.2057257489969627</v>
+        <v>0.224347686889707</v>
       </c>
       <c r="AL7">
-        <v>42.8</v>
+        <v>43</v>
       </c>
       <c r="AM7">
-        <v>42.8</v>
+        <v>43</v>
       </c>
       <c r="AN7">
-        <v>1.852608475434746</v>
+        <v>-4.785998861696073</v>
       </c>
       <c r="AO7">
-        <v>11.53271028037383</v>
+        <v>-5.853488372093023</v>
       </c>
       <c r="AP7">
-        <v>1.852608475434746</v>
+        <v>-4.785998861696073</v>
       </c>
       <c r="AQ7">
-        <v>11.53271028037383</v>
+        <v>-5.853488372093023</v>
       </c>
     </row>
     <row r="8">
@@ -1380,7 +1377,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Heungkuk Fire &amp; Marine Insurance Co., Ltd. (KOSE:A000540)</t>
+          <t>DB Insurance Co., Ltd. (KOSE:A005830)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1389,118 +1386,121 @@
         </is>
       </c>
       <c r="D8">
-        <v>-0.0171</v>
+        <v>0.0429</v>
       </c>
       <c r="E8">
-        <v>0.233</v>
+        <v>0.08990000000000001</v>
       </c>
       <c r="G8">
-        <v>0.04794906922395036</v>
+        <v>0.038670769041901</v>
       </c>
       <c r="H8">
-        <v>0.04794906922395036</v>
+        <v>0.038670769041901</v>
       </c>
       <c r="I8">
-        <v>0.02937384156660488</v>
+        <v>-0.03919251751310126</v>
       </c>
       <c r="J8">
-        <v>0.02345883511415157</v>
+        <v>-0.02933482503830147</v>
       </c>
       <c r="K8">
-        <v>58.3</v>
+        <v>686</v>
       </c>
       <c r="L8">
-        <v>0.02349101458618744</v>
+        <v>0.05263521341814303</v>
       </c>
       <c r="M8">
-        <v>-0</v>
+        <v>146.4</v>
       </c>
       <c r="N8">
-        <v>-0</v>
+        <v>0.04720448829560844</v>
       </c>
       <c r="O8">
-        <v>-0</v>
+        <v>0.2134110787172012</v>
       </c>
       <c r="P8">
-        <v>-0</v>
+        <v>146.4</v>
       </c>
       <c r="Q8">
-        <v>-0</v>
+        <v>0.04720448829560844</v>
       </c>
       <c r="R8">
-        <v>-0</v>
+        <v>0.2134110787172012</v>
       </c>
       <c r="S8">
         <v>0</v>
       </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
       <c r="U8">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="V8">
-        <v>5.14668039114771e-06</v>
+        <v>0</v>
       </c>
       <c r="W8">
-        <v>0.08873668188736682</v>
+        <v>0.1241089843325976</v>
       </c>
       <c r="X8">
-        <v>0.09799471211164629</v>
+        <v>0.1035081850071165</v>
       </c>
       <c r="Y8">
-        <v>-0.00925803022427947</v>
+        <v>0.02060079932548109</v>
       </c>
       <c r="Z8">
-        <v>2.503942362309906</v>
+        <v>1.776042887434113</v>
       </c>
       <c r="AA8">
-        <v>0.05873957101276728</v>
+        <v>-0.05209990736339946</v>
       </c>
       <c r="AB8">
-        <v>0.05176225554945247</v>
+        <v>0.08213486004098641</v>
       </c>
       <c r="AC8">
-        <v>0.006977315463314808</v>
+        <v>-0.1342347674043859</v>
       </c>
       <c r="AD8">
-        <v>325.2</v>
+        <v>1573.4</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>325.2</v>
+        <v>1573.4</v>
       </c>
       <c r="AG8">
-        <v>325.199</v>
+        <v>1573.4</v>
       </c>
       <c r="AH8">
-        <v>0.6259865255052935</v>
+        <v>0.3365705484726619</v>
       </c>
       <c r="AI8">
-        <v>0.3487025520051469</v>
+        <v>0.3014233989156881</v>
       </c>
       <c r="AJ8">
-        <v>0.6259858055549674</v>
+        <v>0.3365705484726619</v>
       </c>
       <c r="AK8">
-        <v>0.3487018536369866</v>
+        <v>0.3014233989156881</v>
       </c>
       <c r="AL8">
-        <v>17</v>
+        <v>73.2</v>
       </c>
       <c r="AM8">
-        <v>17</v>
+        <v>73.2</v>
       </c>
       <c r="AN8">
-        <v>3.621380846325167</v>
+        <v>-3.76772030651341</v>
       </c>
       <c r="AO8">
-        <v>4.288235294117648</v>
+        <v>-6.978142076502732</v>
       </c>
       <c r="AP8">
-        <v>3.621369710467706</v>
+        <v>-3.76772030651341</v>
       </c>
       <c r="AQ8">
-        <v>4.288235294117648</v>
+        <v>-6.978142076502732</v>
       </c>
     </row>
     <row r="9">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Hanwha General Insurance Co., Ltd. (KOSE:A000370)</t>
+          <t>Heungkuk Fire&amp;Marine Insurance Co., Ltd. (KOSE:A000540)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1520,37 +1520,37 @@
         </is>
       </c>
       <c r="D9">
-        <v>0.07099999999999999</v>
+        <v>-0.00549</v>
       </c>
       <c r="E9">
-        <v>0.0388</v>
+        <v>0.117</v>
       </c>
       <c r="G9">
-        <v>0.04680771391125258</v>
+        <v>0.0126865671641791</v>
       </c>
       <c r="H9">
-        <v>0.04680771391125258</v>
+        <v>0.0126865671641791</v>
       </c>
       <c r="I9">
-        <v>0.03578189685660197</v>
+        <v>-0.03283582089552239</v>
       </c>
       <c r="J9">
-        <v>0.02407482129716721</v>
+        <v>-0.02517821341055914</v>
       </c>
       <c r="K9">
-        <v>110.5</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="L9">
-        <v>0.02298778838752627</v>
+        <v>0.04084577114427861</v>
       </c>
       <c r="M9">
-        <v>0.434</v>
+        <v>-0</v>
       </c>
       <c r="N9">
-        <v>0.001194276279581728</v>
+        <v>-0</v>
       </c>
       <c r="O9">
-        <v>0.003927601809954751</v>
+        <v>-0</v>
       </c>
       <c r="P9">
         <v>-0</v>
@@ -1562,79 +1562,76 @@
         <v>-0</v>
       </c>
       <c r="S9">
-        <v>0.434</v>
-      </c>
-      <c r="T9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>5.841121495327103e-06</v>
       </c>
       <c r="W9">
-        <v>0.06796653954976012</v>
+        <v>0.136039768019884</v>
       </c>
       <c r="X9">
-        <v>0.08262407755581838</v>
+        <v>0.1306438668652689</v>
       </c>
       <c r="Y9">
-        <v>-0.01465753800605826</v>
+        <v>0.005395901154615051</v>
       </c>
       <c r="Z9">
-        <v>2.359098939929329</v>
+        <v>2.155267161984947</v>
       </c>
       <c r="AA9">
-        <v>0.05679488540113518</v>
+        <v>-0.05426577656122716</v>
       </c>
       <c r="AB9">
-        <v>0.05118984292352718</v>
+        <v>0.08301392859694183</v>
       </c>
       <c r="AC9">
-        <v>0.005605042477607999</v>
+        <v>-0.137279705158169</v>
       </c>
       <c r="AD9">
-        <v>405.6</v>
+        <v>219</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>405.6</v>
+        <v>219</v>
       </c>
       <c r="AG9">
-        <v>405.6</v>
+        <v>218.999</v>
       </c>
       <c r="AH9">
-        <v>0.5274382314694409</v>
+        <v>0.5612506406970784</v>
       </c>
       <c r="AI9">
-        <v>0.2348309402501158</v>
+        <v>0.3307157958320749</v>
       </c>
       <c r="AJ9">
-        <v>0.5274382314694409</v>
+        <v>0.5612495162724661</v>
       </c>
       <c r="AK9">
-        <v>0.2348309402501158</v>
+        <v>0.3307147851325659</v>
       </c>
       <c r="AL9">
-        <v>19</v>
+        <v>15.1</v>
       </c>
       <c r="AM9">
-        <v>19</v>
+        <v>15.1</v>
       </c>
       <c r="AN9">
-        <v>1.780509218612818</v>
+        <v>-4.591194968553459</v>
       </c>
       <c r="AO9">
-        <v>9.052631578947368</v>
+        <v>-4.370860927152318</v>
       </c>
       <c r="AP9">
-        <v>1.780509218612818</v>
+        <v>-4.591174004192871</v>
       </c>
       <c r="AQ9">
-        <v>9.052631578947368</v>
+        <v>-4.370860927152318</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/south_korea/south_korea_insurance_prop_cas.xlsx
+++ b/research/traditional_assets/database/data/south_korea/south_korea_insurance_prop_cas.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ9"/>
+  <dimension ref="A1:AQ8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,121 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0371</v>
+        <v>0.03395</v>
       </c>
       <c r="E2">
-        <v>0.0481</v>
+        <v>0.108</v>
+      </c>
+      <c r="F2">
+        <v>0.232</v>
       </c>
       <c r="G2">
-        <v>0.05834058827468745</v>
+        <v>0.05926175097852456</v>
       </c>
       <c r="H2">
-        <v>0.05834058827468745</v>
+        <v>0.05926175097852456</v>
       </c>
       <c r="I2">
-        <v>0.01075118959921954</v>
+        <v>0.106360729583526</v>
       </c>
       <c r="J2">
-        <v>0.007936493051489347</v>
+        <v>0.08108986397800508</v>
       </c>
       <c r="K2">
-        <v>2776.2</v>
+        <v>2544.3</v>
       </c>
       <c r="L2">
-        <v>0.05024823664200892</v>
+        <v>0.04651396625575643</v>
       </c>
       <c r="M2">
-        <v>816.4536000000001</v>
+        <v>755.4639999999999</v>
       </c>
       <c r="N2">
-        <v>0.04937431059506531</v>
+        <v>0.04898390035467201</v>
       </c>
       <c r="O2">
-        <v>0.2940903393127296</v>
+        <v>0.296924104861848</v>
       </c>
       <c r="P2">
-        <v>630.0536</v>
+        <v>755.4639999999999</v>
       </c>
       <c r="Q2">
-        <v>0.03810193517174649</v>
+        <v>0.04898390035467201</v>
       </c>
       <c r="R2">
-        <v>0.2269482025790649</v>
+        <v>0.296924104861848</v>
       </c>
       <c r="S2">
-        <v>186.4</v>
+        <v>0</v>
       </c>
       <c r="T2">
-        <v>0.2283044621274253</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>0.021</v>
+        <v>0.031</v>
       </c>
       <c r="V2">
-        <v>1.269956458635704e-06</v>
+        <v>2.010024185129711e-06</v>
       </c>
       <c r="W2">
-        <v>0.1038666249217282</v>
+        <v>0.1784629100232754</v>
       </c>
       <c r="X2">
-        <v>0.1035081850071165</v>
+        <v>0.0955623132088847</v>
       </c>
       <c r="Y2">
-        <v>0.0003584399146117218</v>
+        <v>0.08290059681439071</v>
       </c>
       <c r="Z2">
-        <v>1.710431876951761</v>
+        <v>3.027341080048318</v>
       </c>
       <c r="AA2">
-        <v>0.01507212103651948</v>
+        <v>0.2437180957579784</v>
       </c>
       <c r="AB2">
-        <v>0.08301392859694183</v>
+        <v>0.07100030994536659</v>
       </c>
       <c r="AC2">
-        <v>-0.06722168882782818</v>
+        <v>0.1717443047418793</v>
       </c>
       <c r="AD2">
-        <v>4395.4</v>
+        <v>3846.6</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>4395.4</v>
+        <v>3846.6</v>
       </c>
       <c r="AG2">
-        <v>4395.379</v>
+        <v>3846.569</v>
       </c>
       <c r="AH2">
-        <v>0.2099907316280803</v>
+        <v>0.1996232348865813</v>
       </c>
       <c r="AI2">
-        <v>0.2242207825332857</v>
+        <v>0.1197668553494368</v>
       </c>
       <c r="AJ2">
-        <v>0.2099899390288619</v>
+        <v>0.1996219472570548</v>
       </c>
       <c r="AK2">
-        <v>0.2242199514675805</v>
+        <v>0.1197660057397603</v>
       </c>
       <c r="AL2">
-        <v>253</v>
+        <v>480</v>
       </c>
       <c r="AM2">
-        <v>253</v>
+        <v>480</v>
       </c>
       <c r="AN2">
-        <v>3.989290252314394</v>
+        <v>0.6134536871650932</v>
       </c>
       <c r="AO2">
-        <v>2.347826086956522</v>
+        <v>12.120625</v>
       </c>
       <c r="AP2">
-        <v>3.989271192593937</v>
+        <v>0.6134487433018627</v>
       </c>
       <c r="AQ2">
-        <v>2.347826086956522</v>
+        <v>12.120625</v>
       </c>
     </row>
     <row r="3">
@@ -713,7 +716,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Meritz Fire &amp; Marine Insurance Co., Ltd. (KOSE:A000060)</t>
+          <t>Heungkuk Fire&amp;Marine Insurance Co., Ltd. (KOSE:A000540)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -722,121 +725,118 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.101</v>
+        <v>0.0179</v>
       </c>
       <c r="E3">
-        <v>0.208</v>
+        <v>0.144</v>
       </c>
       <c r="G3">
-        <v>0.0977416440831075</v>
+        <v>0.06788072507044624</v>
       </c>
       <c r="H3">
-        <v>0.0977416440831075</v>
+        <v>0.06788072507044624</v>
       </c>
       <c r="I3">
-        <v>0.09607691315008388</v>
+        <v>0.1423224124153594</v>
       </c>
       <c r="J3">
-        <v>0.06974116494706759</v>
+        <v>0.112443242713763</v>
       </c>
       <c r="K3">
-        <v>638.2</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="L3">
-        <v>0.08235901406633114</v>
+        <v>0.03873491188964125</v>
       </c>
       <c r="M3">
-        <v>233.4016</v>
+        <v>-0</v>
       </c>
       <c r="N3">
-        <v>0.05454327911759208</v>
+        <v>-0</v>
       </c>
       <c r="O3">
-        <v>0.3657185835161391</v>
+        <v>-0</v>
       </c>
       <c r="P3">
-        <v>47.0016</v>
+        <v>-0</v>
       </c>
       <c r="Q3">
-        <v>0.01098373527762199</v>
+        <v>-0</v>
       </c>
       <c r="R3">
-        <v>0.0736471325603259</v>
+        <v>-0</v>
       </c>
       <c r="S3">
-        <v>186.4</v>
-      </c>
-      <c r="T3">
-        <v>0.7986234884422386</v>
+        <v>0</v>
       </c>
       <c r="U3">
-        <v>0.003</v>
+        <v>0.001</v>
       </c>
       <c r="V3">
-        <v>7.010656197420079e-07</v>
+        <v>6.527415143603134e-06</v>
       </c>
       <c r="W3">
-        <v>0.3116363103667171</v>
+        <v>0.2093181818181818</v>
       </c>
       <c r="X3">
-        <v>0.09335633705675071</v>
+        <v>0.1141660258347469</v>
       </c>
       <c r="Y3">
-        <v>0.2182799733099664</v>
+        <v>0.09515215598343485</v>
       </c>
       <c r="Z3">
-        <v>2.711244579872552</v>
+        <v>3.590558267858032</v>
       </c>
       <c r="AA3">
-        <v>0.1890853554567346</v>
+        <v>0.4037340147906689</v>
       </c>
       <c r="AB3">
-        <v>0.08482353275249765</v>
+        <v>0.06804014421695628</v>
       </c>
       <c r="AC3">
-        <v>0.1042618227042369</v>
+        <v>0.3356938705737127</v>
       </c>
       <c r="AD3">
-        <v>935.2</v>
+        <v>233.8</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>935.2</v>
+        <v>233.8</v>
       </c>
       <c r="AG3">
-        <v>935.197</v>
+        <v>233.799</v>
       </c>
       <c r="AH3">
-        <v>0.1793494937097269</v>
+        <v>0.6041343669250646</v>
       </c>
       <c r="AI3">
-        <v>0.6848271821909784</v>
+        <v>0.1813246471226928</v>
       </c>
       <c r="AJ3">
-        <v>0.1793490215647179</v>
+        <v>0.6041333440138088</v>
       </c>
       <c r="AK3">
-        <v>0.6848264898062899</v>
+        <v>0.1813240121948288</v>
       </c>
       <c r="AL3">
-        <v>34.8</v>
+        <v>14.6</v>
       </c>
       <c r="AM3">
-        <v>34.8</v>
+        <v>14.6</v>
       </c>
       <c r="AN3">
-        <v>1.189973279043135</v>
+        <v>0.6474660758792579</v>
       </c>
       <c r="AO3">
-        <v>21.39367816091954</v>
+        <v>23.17808219178082</v>
       </c>
       <c r="AP3">
-        <v>1.189969461763583</v>
+        <v>0.6474633065632789</v>
       </c>
       <c r="AQ3">
-        <v>21.39367816091954</v>
+        <v>23.17808219178082</v>
       </c>
     </row>
     <row r="4">
@@ -856,28 +856,28 @@
         </is>
       </c>
       <c r="D4">
-        <v>-0.0125</v>
+        <v>-0.0131</v>
       </c>
       <c r="E4">
-        <v>0.00444</v>
+        <v>0.229</v>
       </c>
       <c r="G4">
-        <v>0.06924355265587492</v>
+        <v>-0.02531927946015281</v>
       </c>
       <c r="H4">
-        <v>0.06924355265587492</v>
+        <v>-0.02531927946015281</v>
       </c>
       <c r="I4">
-        <v>0.04462362282267495</v>
+        <v>0.2043946238358151</v>
       </c>
       <c r="J4">
-        <v>0.03413936489076894</v>
+        <v>0.1575125003266211</v>
       </c>
       <c r="K4">
-        <v>52.1</v>
+        <v>165.3</v>
       </c>
       <c r="L4">
-        <v>0.03206745860774297</v>
+        <v>0.09218671574368413</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -907,67 +907,67 @@
         <v>0</v>
       </c>
       <c r="W4">
-        <v>0.0586381541924592</v>
+        <v>0.3893075836081017</v>
       </c>
       <c r="X4">
-        <v>0.1180545949926688</v>
+        <v>0.1059335408539258</v>
       </c>
       <c r="Y4">
-        <v>-0.05941644080020958</v>
+        <v>0.2833740427541759</v>
       </c>
       <c r="Z4">
-        <v>1.336211859527922</v>
+        <v>2.412350329611193</v>
       </c>
       <c r="AA4">
-        <v>0.04561742424379661</v>
+        <v>0.3799753320808077</v>
       </c>
       <c r="AB4">
-        <v>0.0806325582045499</v>
+        <v>0.07097578981941885</v>
       </c>
       <c r="AC4">
-        <v>-0.03501513396075329</v>
+        <v>0.3089995422613888</v>
       </c>
       <c r="AD4">
-        <v>318.7</v>
+        <v>696.7</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>318.7</v>
+        <v>696.7</v>
       </c>
       <c r="AG4">
-        <v>318.7</v>
+        <v>696.7</v>
       </c>
       <c r="AH4">
-        <v>0.4794644200391153</v>
+        <v>0.5482804753285591</v>
       </c>
       <c r="AI4">
-        <v>0.4287636216870712</v>
+        <v>0.4105238347769725</v>
       </c>
       <c r="AJ4">
-        <v>0.4794644200391153</v>
+        <v>0.5482804753285591</v>
       </c>
       <c r="AK4">
-        <v>0.4287636216870712</v>
+        <v>0.4105238347769725</v>
       </c>
       <c r="AL4">
-        <v>14.1</v>
+        <v>85.2</v>
       </c>
       <c r="AM4">
-        <v>14.1</v>
+        <v>85.2</v>
       </c>
       <c r="AN4">
-        <v>3.521546961325967</v>
+        <v>1.770520965692503</v>
       </c>
       <c r="AO4">
-        <v>5.141843971631205</v>
+        <v>4.301643192488263</v>
       </c>
       <c r="AP4">
-        <v>3.521546961325967</v>
+        <v>1.770520965692503</v>
       </c>
       <c r="AQ4">
-        <v>5.141843971631205</v>
+        <v>4.301643192488263</v>
       </c>
     </row>
     <row r="5">
@@ -978,7 +978,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Samsung Fire &amp; Marine Insurance Co., Ltd. (KOSE:A000810)</t>
+          <t>DB Insurance Co., Ltd. (KOSE:A005830)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -987,46 +987,49 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.0166</v>
+        <v>0.0526</v>
       </c>
       <c r="E5">
-        <v>0.008529999999999999</v>
+        <v>0.102</v>
+      </c>
+      <c r="F5">
+        <v>0.193</v>
       </c>
       <c r="G5">
-        <v>0.08804562204806145</v>
+        <v>0.05465768578703795</v>
       </c>
       <c r="H5">
-        <v>0.08804562204806145</v>
+        <v>0.05465768578703795</v>
       </c>
       <c r="I5">
-        <v>0.0369349146208543</v>
+        <v>0.1127192035033286</v>
       </c>
       <c r="J5">
-        <v>0.0271572179329883</v>
+        <v>0.08698620918733405</v>
       </c>
       <c r="K5">
-        <v>806.1</v>
+        <v>678.1</v>
       </c>
       <c r="L5">
-        <v>0.05229797062334562</v>
+        <v>0.04438727752358135</v>
       </c>
       <c r="M5">
-        <v>355.9</v>
+        <v>205.2</v>
       </c>
       <c r="N5">
-        <v>0.05576971292465838</v>
+        <v>0.05254936105918205</v>
       </c>
       <c r="O5">
-        <v>0.4415084977049993</v>
+        <v>0.3026102344786905</v>
       </c>
       <c r="P5">
-        <v>355.9</v>
+        <v>205.2</v>
       </c>
       <c r="Q5">
-        <v>0.05576971292465838</v>
+        <v>0.05254936105918205</v>
       </c>
       <c r="R5">
-        <v>0.4415084977049993</v>
+        <v>0.3026102344786905</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -1035,73 +1038,73 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>0.017</v>
+        <v>0</v>
       </c>
       <c r="V5">
-        <v>2.663908737620659e-06</v>
+        <v>0</v>
       </c>
       <c r="W5">
-        <v>0.06229617150187793</v>
+        <v>0.1892178474760722</v>
       </c>
       <c r="X5">
-        <v>0.08567336415958873</v>
+        <v>0.08516524127980163</v>
       </c>
       <c r="Y5">
-        <v>-0.0233771926577108</v>
+        <v>0.1040526061962706</v>
       </c>
       <c r="Z5">
-        <v>1.19118386686834</v>
+        <v>2.964966317125572</v>
       </c>
       <c r="AA5">
-        <v>0.03234923987080324</v>
+        <v>0.2579111802948845</v>
       </c>
       <c r="AB5">
-        <v>0.08567336415958873</v>
+        <v>0.07102483007131433</v>
       </c>
       <c r="AC5">
-        <v>-0.0533241242887855</v>
+        <v>0.1868863502235701</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>1662.7</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>1662.7</v>
       </c>
       <c r="AG5">
-        <v>-0.017</v>
+        <v>1662.7</v>
       </c>
       <c r="AH5">
-        <v>0</v>
+        <v>0.2986385516200876</v>
       </c>
       <c r="AI5">
-        <v>0</v>
+        <v>0.1795805071931568</v>
       </c>
       <c r="AJ5">
-        <v>-2.663915834049326e-06</v>
+        <v>0.2986385516200876</v>
       </c>
       <c r="AK5">
-        <v>-2.348104244226047e-06</v>
+        <v>0.1795805071931568</v>
       </c>
       <c r="AL5">
-        <v>52.1</v>
+        <v>145.1</v>
       </c>
       <c r="AM5">
-        <v>52.1</v>
+        <v>145.1</v>
       </c>
       <c r="AN5">
-        <v>0</v>
+        <v>0.9102704478265631</v>
       </c>
       <c r="AO5">
-        <v>10.92706333973129</v>
+        <v>11.86767746381806</v>
       </c>
       <c r="AP5">
-        <v>-2.179207793872581e-05</v>
+        <v>0.9102704478265631</v>
       </c>
       <c r="AQ5">
-        <v>10.92706333973129</v>
+        <v>11.86767746381806</v>
       </c>
     </row>
     <row r="6">
@@ -1112,7 +1115,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Hanwha General Insurance Co., Ltd. (KOSE:A000370)</t>
+          <t>Hyundai Marine &amp; Fire Insurance Co., Ltd. (KOSE:A001450)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1121,50 +1124,56 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.0371</v>
+        <v>0.0558</v>
       </c>
       <c r="E6">
-        <v>0.0481</v>
+        <v>-0.0351</v>
+      </c>
+      <c r="F6">
+        <v>0.242</v>
       </c>
       <c r="G6">
-        <v>0.03055464967513735</v>
+        <v>0.04320601127113338</v>
       </c>
       <c r="H6">
-        <v>0.03055464967513735</v>
+        <v>0.04320601127113338</v>
       </c>
       <c r="I6">
-        <v>0.009081102777011263</v>
+        <v>0.08286621753136529</v>
       </c>
       <c r="J6">
-        <v>0.006364145731297087</v>
+        <v>0.06490374626059581</v>
       </c>
       <c r="K6">
-        <v>132.7</v>
+        <v>266.3</v>
       </c>
       <c r="L6">
-        <v>0.03328901487595012</v>
+        <v>0.02009038030644808</v>
       </c>
       <c r="M6">
-        <v>-0</v>
+        <v>114.464</v>
       </c>
       <c r="N6">
-        <v>-0</v>
+        <v>0.06060144006776789</v>
       </c>
       <c r="O6">
-        <v>-0</v>
+        <v>0.4298310176492677</v>
       </c>
       <c r="P6">
-        <v>-0</v>
+        <v>114.464</v>
       </c>
       <c r="Q6">
-        <v>-0</v>
+        <v>0.06060144006776789</v>
       </c>
       <c r="R6">
-        <v>-0</v>
+        <v>0.4298310176492677</v>
       </c>
       <c r="S6">
         <v>0</v>
       </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
       <c r="U6">
         <v>0</v>
       </c>
@@ -1172,67 +1181,67 @@
         <v>0</v>
       </c>
       <c r="W6">
-        <v>0.1038666249217282</v>
+        <v>0.09159701441199739</v>
       </c>
       <c r="X6">
-        <v>0.127231360785379</v>
+        <v>0.08519108556384355</v>
       </c>
       <c r="Y6">
-        <v>-0.02336473586365079</v>
+        <v>0.00640592884815383</v>
       </c>
       <c r="Z6">
-        <v>2.368286596958175</v>
+        <v>3.536390800917774</v>
       </c>
       <c r="AA6">
-        <v>0.01507212103651948</v>
+        <v>0.2295250112210724</v>
       </c>
       <c r="AB6">
-        <v>0.08229380986434766</v>
+        <v>0.07292275196088395</v>
       </c>
       <c r="AC6">
-        <v>-0.06722168882782818</v>
+        <v>0.1566022592601884</v>
       </c>
       <c r="AD6">
-        <v>508.2</v>
+        <v>806.1</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>508.2</v>
+        <v>806.1</v>
       </c>
       <c r="AG6">
-        <v>508.2</v>
+        <v>806.1</v>
       </c>
       <c r="AH6">
-        <v>0.5417332906939559</v>
+        <v>0.2991205610597796</v>
       </c>
       <c r="AI6">
-        <v>0.8145536143612758</v>
+        <v>0.1395385068116118</v>
       </c>
       <c r="AJ6">
-        <v>0.5417332906939559</v>
+        <v>0.2991205610597796</v>
       </c>
       <c r="AK6">
-        <v>0.8145536143612758</v>
+        <v>0.1395385068116118</v>
       </c>
       <c r="AL6">
-        <v>20.7</v>
+        <v>76.3</v>
       </c>
       <c r="AM6">
-        <v>20.7</v>
+        <v>76.3</v>
       </c>
       <c r="AN6">
-        <v>5.888760139049826</v>
+        <v>0.692228424216402</v>
       </c>
       <c r="AO6">
-        <v>1.748792270531401</v>
+        <v>14.39580602883355</v>
       </c>
       <c r="AP6">
-        <v>5.888760139049826</v>
+        <v>0.692228424216402</v>
       </c>
       <c r="AQ6">
-        <v>1.748792270531401</v>
+        <v>14.39580602883355</v>
       </c>
     </row>
     <row r="7">
@@ -1243,7 +1252,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Hyundai Marine &amp; Fire Insurance Co., Ltd. (KOSE:A001450)</t>
+          <t>Hanwha General Insurance Co., Ltd. (KOSE:A000370)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1252,53 +1261,50 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.0451</v>
+        <v>0.0372</v>
       </c>
       <c r="E7">
-        <v>0.036</v>
+        <v>0.06709999999999999</v>
       </c>
       <c r="G7">
-        <v>0.030175806874836</v>
+        <v>0.05367599938125649</v>
       </c>
       <c r="H7">
-        <v>0.030175806874836</v>
+        <v>0.05367599938125649</v>
       </c>
       <c r="I7">
-        <v>-0.02201521910259774</v>
+        <v>0.03842839148785716</v>
       </c>
       <c r="J7">
-        <v>-0.01596282387580743</v>
+        <v>0.02725142714974855</v>
       </c>
       <c r="K7">
-        <v>379</v>
+        <v>131.9</v>
       </c>
       <c r="L7">
-        <v>0.03314965450887781</v>
+        <v>0.02914723885709235</v>
       </c>
       <c r="M7">
-        <v>80.75200000000001</v>
+        <v>-0</v>
       </c>
       <c r="N7">
-        <v>0.04420649258225216</v>
+        <v>-0</v>
       </c>
       <c r="O7">
-        <v>0.213065963060686</v>
+        <v>-0</v>
       </c>
       <c r="P7">
-        <v>80.75200000000001</v>
+        <v>-0</v>
       </c>
       <c r="Q7">
-        <v>0.04420649258225216</v>
+        <v>-0</v>
       </c>
       <c r="R7">
-        <v>0.213065963060686</v>
+        <v>-0</v>
       </c>
       <c r="S7">
         <v>0</v>
       </c>
-      <c r="T7">
-        <v>0</v>
-      </c>
       <c r="U7">
         <v>0</v>
       </c>
@@ -1306,67 +1312,67 @@
         <v>0</v>
       </c>
       <c r="W7">
-        <v>0.0894606396789803</v>
+        <v>-1.365424430641822</v>
       </c>
       <c r="X7">
-        <v>0.1018565682660915</v>
+        <v>0.106066327493267</v>
       </c>
       <c r="Y7">
-        <v>-0.01239592858711121</v>
+        <v>-1.471490758135089</v>
       </c>
       <c r="Z7">
-        <v>2.143499943754922</v>
+        <v>8.320095605809891</v>
       </c>
       <c r="AA7">
-        <v>-0.03421631207996294</v>
+        <v>0.2267344792806713</v>
       </c>
       <c r="AB7">
-        <v>0.08507808606671824</v>
+        <v>0.07042024712263817</v>
       </c>
       <c r="AC7">
-        <v>-0.1192943981466812</v>
+        <v>0.1563142321580331</v>
       </c>
       <c r="AD7">
-        <v>840.9</v>
+        <v>447.3</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>840.9</v>
+        <v>447.3</v>
       </c>
       <c r="AG7">
-        <v>840.9</v>
+        <v>447.3</v>
       </c>
       <c r="AH7">
-        <v>0.3152271704903284</v>
+        <v>0.54930615252364</v>
       </c>
       <c r="AI7">
-        <v>0.224347686889707</v>
+        <v>0.1467327122424879</v>
       </c>
       <c r="AJ7">
-        <v>0.3152271704903284</v>
+        <v>0.54930615252364</v>
       </c>
       <c r="AK7">
-        <v>0.224347686889707</v>
+        <v>0.1467327122424879</v>
       </c>
       <c r="AL7">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="AM7">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="AN7">
-        <v>-4.785998861696073</v>
+        <v>1.90016992353441</v>
       </c>
       <c r="AO7">
-        <v>-5.853488372093023</v>
+        <v>6.440740740740741</v>
       </c>
       <c r="AP7">
-        <v>-4.785998861696073</v>
+        <v>1.90016992353441</v>
       </c>
       <c r="AQ7">
-        <v>-5.853488372093023</v>
+        <v>6.440740740740741</v>
       </c>
     </row>
     <row r="8">
@@ -1377,7 +1383,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>DB Insurance Co., Ltd. (KOSE:A005830)</t>
+          <t>Samsung Fire &amp; Marine Insurance Co., Ltd. (KOSE:A000810)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1386,46 +1392,49 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.0429</v>
+        <v>0.0307</v>
       </c>
       <c r="E8">
-        <v>0.08990000000000001</v>
+        <v>0.114</v>
+      </c>
+      <c r="F8">
+        <v>0.232</v>
       </c>
       <c r="G8">
-        <v>0.038670769041901</v>
+        <v>0.08442272030037318</v>
       </c>
       <c r="H8">
-        <v>0.038670769041901</v>
+        <v>0.08442272030037318</v>
       </c>
       <c r="I8">
-        <v>-0.03919251751310126</v>
+        <v>0.1212653677968818</v>
       </c>
       <c r="J8">
-        <v>-0.02933482503830147</v>
+        <v>0.09090597953793611</v>
       </c>
       <c r="K8">
-        <v>686</v>
+        <v>1210.6</v>
       </c>
       <c r="L8">
-        <v>0.05263521341814303</v>
+        <v>0.06928958996314018</v>
       </c>
       <c r="M8">
-        <v>146.4</v>
+        <v>435.8</v>
       </c>
       <c r="N8">
-        <v>0.04720448829560844</v>
+        <v>0.05106153629844871</v>
       </c>
       <c r="O8">
-        <v>0.2134110787172012</v>
+        <v>0.3599867834131836</v>
       </c>
       <c r="P8">
-        <v>146.4</v>
+        <v>435.8</v>
       </c>
       <c r="Q8">
-        <v>0.04720448829560844</v>
+        <v>0.05106153629844871</v>
       </c>
       <c r="R8">
-        <v>0.2134110787172012</v>
+        <v>0.3599867834131836</v>
       </c>
       <c r="S8">
         <v>0</v>
@@ -1434,204 +1443,73 @@
         <v>0</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>3.515020855790411e-06</v>
       </c>
       <c r="W8">
-        <v>0.1241089843325976</v>
+        <v>0.1677079725704786</v>
       </c>
       <c r="X8">
-        <v>0.1035081850071165</v>
+        <v>0.07394252064490406</v>
       </c>
       <c r="Y8">
-        <v>0.02060079932548109</v>
+        <v>0.09376545192557456</v>
       </c>
       <c r="Z8">
-        <v>1.776042887434113</v>
+        <v>2.420397748391178</v>
       </c>
       <c r="AA8">
-        <v>-0.05209990736339946</v>
+        <v>0.2200286281889151</v>
       </c>
       <c r="AB8">
-        <v>0.08213486004098641</v>
+        <v>0.07394252064490406</v>
       </c>
       <c r="AC8">
-        <v>-0.1342347674043859</v>
+        <v>0.146086107544011</v>
       </c>
       <c r="AD8">
-        <v>1573.4</v>
+        <v>0</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>1573.4</v>
+        <v>0</v>
       </c>
       <c r="AG8">
-        <v>1573.4</v>
+        <v>-0.03</v>
       </c>
       <c r="AH8">
-        <v>0.3365705484726619</v>
+        <v>0</v>
       </c>
       <c r="AI8">
-        <v>0.3014233989156881</v>
+        <v>0</v>
       </c>
       <c r="AJ8">
-        <v>0.3365705484726619</v>
+        <v>-3.515033211205458e-06</v>
       </c>
       <c r="AK8">
-        <v>0.3014233989156881</v>
+        <v>-2.715725954283469e-06</v>
       </c>
       <c r="AL8">
-        <v>73.2</v>
+        <v>131.8</v>
       </c>
       <c r="AM8">
-        <v>73.2</v>
+        <v>131.8</v>
       </c>
       <c r="AN8">
-        <v>-3.76772030651341</v>
+        <v>0</v>
       </c>
       <c r="AO8">
-        <v>-6.978142076502732</v>
+        <v>16.07511380880121</v>
       </c>
       <c r="AP8">
-        <v>-3.76772030651341</v>
+        <v>-1.310444240597562e-05</v>
       </c>
       <c r="AQ8">
-        <v>-6.978142076502732</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>South Korea</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Heungkuk Fire&amp;Marine Insurance Co., Ltd. (KOSE:A000540)</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Insurance (Prop/Cas.)</t>
-        </is>
-      </c>
-      <c r="D9">
-        <v>-0.00549</v>
-      </c>
-      <c r="E9">
-        <v>0.117</v>
-      </c>
-      <c r="G9">
-        <v>0.0126865671641791</v>
-      </c>
-      <c r="H9">
-        <v>0.0126865671641791</v>
-      </c>
-      <c r="I9">
-        <v>-0.03283582089552239</v>
-      </c>
-      <c r="J9">
-        <v>-0.02517821341055914</v>
-      </c>
-      <c r="K9">
-        <v>82.09999999999999</v>
-      </c>
-      <c r="L9">
-        <v>0.04084577114427861</v>
-      </c>
-      <c r="M9">
-        <v>-0</v>
-      </c>
-      <c r="N9">
-        <v>-0</v>
-      </c>
-      <c r="O9">
-        <v>-0</v>
-      </c>
-      <c r="P9">
-        <v>-0</v>
-      </c>
-      <c r="Q9">
-        <v>-0</v>
-      </c>
-      <c r="R9">
-        <v>-0</v>
-      </c>
-      <c r="S9">
-        <v>0</v>
-      </c>
-      <c r="U9">
-        <v>0.001</v>
-      </c>
-      <c r="V9">
-        <v>5.841121495327103e-06</v>
-      </c>
-      <c r="W9">
-        <v>0.136039768019884</v>
-      </c>
-      <c r="X9">
-        <v>0.1306438668652689</v>
-      </c>
-      <c r="Y9">
-        <v>0.005395901154615051</v>
-      </c>
-      <c r="Z9">
-        <v>2.155267161984947</v>
-      </c>
-      <c r="AA9">
-        <v>-0.05426577656122716</v>
-      </c>
-      <c r="AB9">
-        <v>0.08301392859694183</v>
-      </c>
-      <c r="AC9">
-        <v>-0.137279705158169</v>
-      </c>
-      <c r="AD9">
-        <v>219</v>
-      </c>
-      <c r="AE9">
-        <v>0</v>
-      </c>
-      <c r="AF9">
-        <v>219</v>
-      </c>
-      <c r="AG9">
-        <v>218.999</v>
-      </c>
-      <c r="AH9">
-        <v>0.5612506406970784</v>
-      </c>
-      <c r="AI9">
-        <v>0.3307157958320749</v>
-      </c>
-      <c r="AJ9">
-        <v>0.5612495162724661</v>
-      </c>
-      <c r="AK9">
-        <v>0.3307147851325659</v>
-      </c>
-      <c r="AL9">
-        <v>15.1</v>
-      </c>
-      <c r="AM9">
-        <v>15.1</v>
-      </c>
-      <c r="AN9">
-        <v>-4.591194968553459</v>
-      </c>
-      <c r="AO9">
-        <v>-4.370860927152318</v>
-      </c>
-      <c r="AP9">
-        <v>-4.591174004192871</v>
-      </c>
-      <c r="AQ9">
-        <v>-4.370860927152318</v>
+        <v>16.07511380880121</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/south_korea/south_korea_insurance_prop_cas.xlsx
+++ b/research/traditional_assets/database/data/south_korea/south_korea_insurance_prop_cas.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ3"/>
+  <dimension ref="A1:AQ8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,118 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0132</v>
+        <v>0.012</v>
+      </c>
+      <c r="E2">
+        <v>0.283</v>
+      </c>
+      <c r="F2">
+        <v>0.0492</v>
       </c>
       <c r="G2">
-        <v>0.08296478490173356</v>
+        <v>0.1447189511244427</v>
       </c>
       <c r="H2">
-        <v>0.08296478490173356</v>
+        <v>0.1447189511244427</v>
       </c>
       <c r="I2">
-        <v>0.1040607336281721</v>
+        <v>0.1606111298815812</v>
       </c>
       <c r="J2">
-        <v>0.07141969921933526</v>
+        <v>0.1203337311862914</v>
       </c>
       <c r="K2">
-        <v>257.3</v>
+        <v>4363.7</v>
       </c>
       <c r="L2">
-        <v>0.06085187900574699</v>
+        <v>0.08989979315857567</v>
       </c>
       <c r="M2">
-        <v>21.3312</v>
+        <v>905.5192000000001</v>
       </c>
       <c r="N2">
-        <v>0.06763221306277742</v>
+        <v>0.05470919252031538</v>
       </c>
       <c r="O2">
-        <v>0.08290400310921102</v>
+        <v>0.2075117904530559</v>
       </c>
       <c r="P2">
-        <v>17.5712</v>
+        <v>901.7592000000001</v>
       </c>
       <c r="Q2">
-        <v>0.05571084337349397</v>
+        <v>0.05448202277739178</v>
       </c>
       <c r="R2">
-        <v>0.06829071123202486</v>
+        <v>0.2066501363521782</v>
       </c>
       <c r="S2">
         <v>3.759999999999998</v>
       </c>
       <c r="T2">
-        <v>0.1762676267626762</v>
+        <v>0.004152313943205178</v>
       </c>
       <c r="U2">
-        <v>0</v>
+        <v>0.028</v>
       </c>
       <c r="V2">
-        <v>0</v>
+        <v>1.691689574962994E-06</v>
       </c>
       <c r="W2">
-        <v>0.1072083333333333</v>
+        <v>0.1378840807386774</v>
       </c>
       <c r="X2">
-        <v>0.1145958189441398</v>
+        <v>0.1074488588644809</v>
       </c>
       <c r="Y2">
-        <v>-0.007387485610806446</v>
+        <v>0.03043522187419651</v>
       </c>
       <c r="Z2">
-        <v>1.414904296613573</v>
+        <v>1.515174548204096</v>
       </c>
       <c r="AA2">
-        <v>0.1010520392882865</v>
+        <v>0.1969978632816886</v>
       </c>
       <c r="AB2">
-        <v>0.07305128397350807</v>
+        <v>0.07397021132229825</v>
       </c>
       <c r="AC2">
-        <v>0.0280007553147784</v>
+        <v>0.1196273335842837</v>
       </c>
       <c r="AD2">
-        <v>457.2</v>
+        <v>4629.3</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>457.2</v>
+        <v>4629.3</v>
       </c>
       <c r="AG2">
-        <v>457.2</v>
+        <v>4629.272</v>
       </c>
       <c r="AH2">
-        <v>0.591768055915092</v>
+        <v>0.2185611497205016</v>
       </c>
       <c r="AI2">
-        <v>0.1686711429203866</v>
+        <v>0.1439320214780292</v>
       </c>
       <c r="AJ2">
-        <v>0.591768055915092</v>
+        <v>0.218560116694519</v>
       </c>
       <c r="AK2">
-        <v>0.1686711429203866</v>
+        <v>0.1439312762164012</v>
       </c>
       <c r="AL2">
-        <v>15.3</v>
+        <v>1182.2</v>
       </c>
       <c r="AM2">
-        <v>15.3</v>
+        <v>1182.2</v>
       </c>
       <c r="AN2">
-        <v>0.8978790259230165</v>
+        <v>0.5563594409124233</v>
       </c>
       <c r="AO2">
-        <v>28.75816993464052</v>
+        <v>6.594484858737946</v>
       </c>
       <c r="AP2">
-        <v>0.8978790259230165</v>
+        <v>0.5563560758109294</v>
       </c>
       <c r="AQ2">
-        <v>28.75816993464052</v>
+        <v>6.594484858737946</v>
       </c>
     </row>
     <row r="3">
@@ -710,126 +716,799 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>Heungkuk Fire&amp;Marine Insurance Co., Ltd. (KOSE:A000540)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Insurance (Prop/Cas.)</t>
+        </is>
+      </c>
+      <c r="D3">
+        <v>0.0191</v>
+      </c>
+      <c r="E3">
+        <v>0.461</v>
+      </c>
+      <c r="G3">
+        <v>0.1622367527173913</v>
+      </c>
+      <c r="H3">
+        <v>0.1622367527173913</v>
+      </c>
+      <c r="I3">
+        <v>0.1507727581521739</v>
+      </c>
+      <c r="J3">
+        <v>0.1156272885309133</v>
+      </c>
+      <c r="K3">
+        <v>265.5</v>
+      </c>
+      <c r="L3">
+        <v>0.1127292798913044</v>
+      </c>
+      <c r="M3">
+        <v>-0</v>
+      </c>
+      <c r="N3">
+        <v>-0</v>
+      </c>
+      <c r="O3">
+        <v>-0</v>
+      </c>
+      <c r="P3">
+        <v>-0</v>
+      </c>
+      <c r="Q3">
+        <v>-0</v>
+      </c>
+      <c r="R3">
+        <v>-0</v>
+      </c>
+      <c r="S3">
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <v>0.001</v>
+      </c>
+      <c r="V3">
+        <v>6.265664160401003E-06</v>
+      </c>
+      <c r="W3">
+        <v>0.2523284546664132</v>
+      </c>
+      <c r="X3">
+        <v>0.1276508117517027</v>
+      </c>
+      <c r="Y3">
+        <v>0.1246776429147105</v>
+      </c>
+      <c r="Z3">
+        <v>1.826559093669319</v>
+      </c>
+      <c r="AA3">
+        <v>0.2112000753424658</v>
+      </c>
+      <c r="AB3">
+        <v>0.07283563253337196</v>
+      </c>
+      <c r="AC3">
+        <v>0.1383644428090939</v>
+      </c>
+      <c r="AD3">
+        <v>315.9</v>
+      </c>
+      <c r="AE3">
+        <v>0</v>
+      </c>
+      <c r="AF3">
+        <v>315.9</v>
+      </c>
+      <c r="AG3">
+        <v>315.899</v>
+      </c>
+      <c r="AH3">
+        <v>0.6643533123028391</v>
+      </c>
+      <c r="AI3">
+        <v>0.3081049448941773</v>
+      </c>
+      <c r="AJ3">
+        <v>0.6643526064197821</v>
+      </c>
+      <c r="AK3">
+        <v>0.3081042700714621</v>
+      </c>
+      <c r="AL3">
+        <v>12.5</v>
+      </c>
+      <c r="AM3">
+        <v>12.5</v>
+      </c>
+      <c r="AN3">
+        <v>0.8332893695594829</v>
+      </c>
+      <c r="AO3">
+        <v>28.408</v>
+      </c>
+      <c r="AP3">
+        <v>0.8332867317330519</v>
+      </c>
+      <c r="AQ3">
+        <v>28.408</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Lotte Non - Life Insurance Co., Ltd. (KOSE:A000400)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Insurance (Prop/Cas.)</t>
+        </is>
+      </c>
+      <c r="D4">
+        <v>-0.00383</v>
+      </c>
+      <c r="E4">
+        <v>0.14</v>
+      </c>
+      <c r="G4">
+        <v>0.3588619263540784</v>
+      </c>
+      <c r="H4">
+        <v>0.3588619263540784</v>
+      </c>
+      <c r="I4">
+        <v>0.2285614629528128</v>
+      </c>
+      <c r="J4">
+        <v>0.1741597499997874</v>
+      </c>
+      <c r="K4">
+        <v>93.8</v>
+      </c>
+      <c r="L4">
+        <v>0.04673875130798744</v>
+      </c>
+      <c r="M4">
+        <v>-0</v>
+      </c>
+      <c r="N4">
+        <v>-0</v>
+      </c>
+      <c r="O4">
+        <v>-0</v>
+      </c>
+      <c r="P4">
+        <v>-0</v>
+      </c>
+      <c r="Q4">
+        <v>-0</v>
+      </c>
+      <c r="R4">
+        <v>-0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>0</v>
+      </c>
+      <c r="V4">
+        <v>0</v>
+      </c>
+      <c r="W4">
+        <v>0.09376249500199919</v>
+      </c>
+      <c r="X4">
+        <v>0.109388624472219</v>
+      </c>
+      <c r="Y4">
+        <v>-0.01562612947021978</v>
+      </c>
+      <c r="Z4">
+        <v>1.182546697307171</v>
+      </c>
+      <c r="AA4">
+        <v>0.2059520371660913</v>
+      </c>
+      <c r="AB4">
+        <v>0.07382058825903004</v>
+      </c>
+      <c r="AC4">
+        <v>0.1321314489070612</v>
+      </c>
+      <c r="AD4">
+        <v>523</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>523</v>
+      </c>
+      <c r="AG4">
+        <v>523</v>
+      </c>
+      <c r="AH4">
+        <v>0.5536149042023922</v>
+      </c>
+      <c r="AI4">
+        <v>0.4387952009396761</v>
+      </c>
+      <c r="AJ4">
+        <v>0.5536149042023922</v>
+      </c>
+      <c r="AK4">
+        <v>0.4387952009396761</v>
+      </c>
+      <c r="AL4">
+        <v>270.4</v>
+      </c>
+      <c r="AM4">
+        <v>270.4</v>
+      </c>
+      <c r="AN4">
+        <v>1.070843570843571</v>
+      </c>
+      <c r="AO4">
+        <v>1.696375739644971</v>
+      </c>
+      <c r="AP4">
+        <v>1.070843570843571</v>
+      </c>
+      <c r="AQ4">
+        <v>1.696375739644971</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>DB Insurance Co., Ltd. (KOSE:A005830)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Insurance (Prop/Cas.)</t>
+        </is>
+      </c>
+      <c r="D5">
+        <v>0.0297</v>
+      </c>
+      <c r="E5">
+        <v>0.383</v>
+      </c>
+      <c r="F5">
+        <v>0.0492</v>
+      </c>
+      <c r="G5">
+        <v>0.1428755632284361</v>
+      </c>
+      <c r="H5">
+        <v>0.1428755632284361</v>
+      </c>
+      <c r="I5">
+        <v>0.1753117903679879</v>
+      </c>
+      <c r="J5">
+        <v>0.1353812907610145</v>
+      </c>
+      <c r="K5">
+        <v>1521.6</v>
+      </c>
+      <c r="L5">
+        <v>0.108999477066126</v>
+      </c>
+      <c r="M5">
+        <v>242.4</v>
+      </c>
+      <c r="N5">
+        <v>0.05800708337321719</v>
+      </c>
+      <c r="O5">
+        <v>0.1593059936908517</v>
+      </c>
+      <c r="P5">
+        <v>242.4</v>
+      </c>
+      <c r="Q5">
+        <v>0.05800708337321719</v>
+      </c>
+      <c r="R5">
+        <v>0.1593059936908517</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>0</v>
+      </c>
+      <c r="V5">
+        <v>0</v>
+      </c>
+      <c r="W5">
+        <v>0.2001525874089079</v>
+      </c>
+      <c r="X5">
+        <v>0.08864511397870359</v>
+      </c>
+      <c r="Y5">
+        <v>0.1115074734302043</v>
+      </c>
+      <c r="Z5">
+        <v>1.507533509863974</v>
+      </c>
+      <c r="AA5">
+        <v>0.2040918324308673</v>
+      </c>
+      <c r="AB5">
+        <v>0.07620028726236082</v>
+      </c>
+      <c r="AC5">
+        <v>0.1278915451685065</v>
+      </c>
+      <c r="AD5">
+        <v>1674.4</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>1674.4</v>
+      </c>
+      <c r="AG5">
+        <v>1674.4</v>
+      </c>
+      <c r="AH5">
+        <v>0.2860657418164423</v>
+      </c>
+      <c r="AI5">
+        <v>0.1820138488798061</v>
+      </c>
+      <c r="AJ5">
+        <v>0.2860657418164423</v>
+      </c>
+      <c r="AK5">
+        <v>0.1820138488798061</v>
+      </c>
+      <c r="AL5">
+        <v>336</v>
+      </c>
+      <c r="AM5">
+        <v>336</v>
+      </c>
+      <c r="AN5">
+        <v>0.6567304675243176</v>
+      </c>
+      <c r="AO5">
+        <v>7.283630952380953</v>
+      </c>
+      <c r="AP5">
+        <v>0.6567304675243176</v>
+      </c>
+      <c r="AQ5">
+        <v>7.283630952380953</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Samsung Fire &amp; Marine Insurance Co., Ltd. (KOSE:A000810)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Insurance (Prop/Cas.)</t>
+        </is>
+      </c>
+      <c r="D6">
+        <v>-0.0144</v>
+      </c>
+      <c r="E6">
+        <v>0.22</v>
+      </c>
+      <c r="F6">
+        <v>0.0475</v>
+      </c>
+      <c r="G6">
+        <v>0.177412334394298</v>
+      </c>
+      <c r="H6">
+        <v>0.177412334394298</v>
+      </c>
+      <c r="I6">
+        <v>0.1875391060692619</v>
+      </c>
+      <c r="J6">
+        <v>0.1423784543520328</v>
+      </c>
+      <c r="K6">
+        <v>1556.6</v>
+      </c>
+      <c r="L6">
+        <v>0.10586523028374</v>
+      </c>
+      <c r="M6">
+        <v>518.7</v>
+      </c>
+      <c r="N6">
+        <v>0.05102904139776485</v>
+      </c>
+      <c r="O6">
+        <v>0.3332262623666967</v>
+      </c>
+      <c r="P6">
+        <v>518.7</v>
+      </c>
+      <c r="Q6">
+        <v>0.05102904139776485</v>
+      </c>
+      <c r="R6">
+        <v>0.3332262623666967</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <v>0.027</v>
+      </c>
+      <c r="V6">
+        <v>2.656225405320321E-06</v>
+      </c>
+      <c r="W6">
+        <v>0.1412022968278014</v>
+      </c>
+      <c r="X6">
+        <v>0.07932442460345521</v>
+      </c>
+      <c r="Y6">
+        <v>0.06187787222434621</v>
+      </c>
+      <c r="Z6">
+        <v>1.333796570532853</v>
+      </c>
+      <c r="AA6">
+        <v>0.1899038941325097</v>
+      </c>
+      <c r="AB6">
+        <v>0.07854077213244878</v>
+      </c>
+      <c r="AC6">
+        <v>0.111363122000061</v>
+      </c>
+      <c r="AD6">
+        <v>238.5</v>
+      </c>
+      <c r="AE6">
+        <v>0</v>
+      </c>
+      <c r="AF6">
+        <v>238.5</v>
+      </c>
+      <c r="AG6">
+        <v>238.473</v>
+      </c>
+      <c r="AH6">
+        <v>0.02292541789624446</v>
+      </c>
+      <c r="AI6">
+        <v>0.0189681637067848</v>
+      </c>
+      <c r="AJ6">
+        <v>0.02292288205836759</v>
+      </c>
+      <c r="AK6">
+        <v>0.01896605709405676</v>
+      </c>
+      <c r="AL6">
+        <v>377.3</v>
+      </c>
+      <c r="AM6">
+        <v>377.3</v>
+      </c>
+      <c r="AN6">
+        <v>0.08118872549019608</v>
+      </c>
+      <c r="AO6">
+        <v>7.3085078187119</v>
+      </c>
+      <c r="AP6">
+        <v>0.0811795343137255</v>
+      </c>
+      <c r="AQ6">
+        <v>7.3085078187119</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Hyundai Marine &amp; Fire Insurance Co., Ltd. (KOSE:A001450)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Insurance (Prop/Cas.)</t>
+        </is>
+      </c>
+      <c r="D7">
+        <v>0.0108</v>
+      </c>
+      <c r="E7">
+        <v>0.283</v>
+      </c>
+      <c r="F7">
+        <v>0.09329999999999999</v>
+      </c>
+      <c r="G7">
+        <v>0.08580618293623016</v>
+      </c>
+      <c r="H7">
+        <v>0.08580618293623016</v>
+      </c>
+      <c r="I7">
+        <v>0.1185018474379536</v>
+      </c>
+      <c r="J7">
+        <v>0.08872384794184816</v>
+      </c>
+      <c r="K7">
+        <v>668.9</v>
+      </c>
+      <c r="L7">
+        <v>0.05926864494634898</v>
+      </c>
+      <c r="M7">
+        <v>123.088</v>
+      </c>
+      <c r="N7">
+        <v>0.09387431360585723</v>
+      </c>
+      <c r="O7">
+        <v>0.1840155479144865</v>
+      </c>
+      <c r="P7">
+        <v>123.088</v>
+      </c>
+      <c r="Q7">
+        <v>0.09387431360585723</v>
+      </c>
+      <c r="R7">
+        <v>0.1840155479144865</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <v>0</v>
+      </c>
+      <c r="V7">
+        <v>0</v>
+      </c>
+      <c r="W7">
+        <v>0.1345658646495534</v>
+      </c>
+      <c r="X7">
+        <v>0.1055090932567428</v>
+      </c>
+      <c r="Y7">
+        <v>0.02905677139281054</v>
+      </c>
+      <c r="Z7">
+        <v>1.95362564697329</v>
+      </c>
+      <c r="AA7">
+        <v>0.1733331848373529</v>
+      </c>
+      <c r="AB7">
+        <v>0.07411983438556645</v>
+      </c>
+      <c r="AC7">
+        <v>0.09921335045178643</v>
+      </c>
+      <c r="AD7">
+        <v>1420.3</v>
+      </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
+      <c r="AF7">
+        <v>1420.3</v>
+      </c>
+      <c r="AG7">
+        <v>1420.3</v>
+      </c>
+      <c r="AH7">
+        <v>0.5199707120629691</v>
+      </c>
+      <c r="AI7">
+        <v>0.2600186734525749</v>
+      </c>
+      <c r="AJ7">
+        <v>0.5199707120629691</v>
+      </c>
+      <c r="AK7">
+        <v>0.2600186734525749</v>
+      </c>
+      <c r="AL7">
+        <v>170.7</v>
+      </c>
+      <c r="AM7">
+        <v>170.7</v>
+      </c>
+      <c r="AN7">
+        <v>0.974945085118067</v>
+      </c>
+      <c r="AO7">
+        <v>7.834797891036908</v>
+      </c>
+      <c r="AP7">
+        <v>0.974945085118067</v>
+      </c>
+      <c r="AQ7">
+        <v>7.834797891036908</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
           <t>Hanwha General Insurance Co., Ltd. (KOSE:A000370)</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Insurance (Prop/Cas.)</t>
         </is>
       </c>
-      <c r="D3">
+      <c r="D8">
         <v>0.0132</v>
       </c>
-      <c r="G3">
+      <c r="G8">
         <v>0.08296478490173356</v>
       </c>
-      <c r="H3">
+      <c r="H8">
         <v>0.08296478490173356</v>
       </c>
-      <c r="I3">
+      <c r="I8">
         <v>0.1040607336281721</v>
       </c>
-      <c r="J3">
+      <c r="J8">
         <v>0.07141969921933526</v>
       </c>
-      <c r="K3">
+      <c r="K8">
         <v>257.3</v>
       </c>
-      <c r="L3">
+      <c r="L8">
         <v>0.06085187900574699</v>
       </c>
-      <c r="M3">
+      <c r="M8">
         <v>21.3312</v>
       </c>
-      <c r="N3">
+      <c r="N8">
         <v>0.06763221306277742</v>
       </c>
-      <c r="O3">
+      <c r="O8">
         <v>0.08290400310921102</v>
       </c>
-      <c r="P3">
+      <c r="P8">
         <v>17.5712</v>
       </c>
-      <c r="Q3">
+      <c r="Q8">
         <v>0.05571084337349397</v>
       </c>
-      <c r="R3">
+      <c r="R8">
         <v>0.06829071123202486</v>
       </c>
-      <c r="S3">
+      <c r="S8">
         <v>3.759999999999998</v>
       </c>
-      <c r="T3">
+      <c r="T8">
         <v>0.1762676267626762</v>
       </c>
-      <c r="U3">
-        <v>0</v>
-      </c>
-      <c r="V3">
-        <v>0</v>
-      </c>
-      <c r="W3">
+      <c r="U8">
+        <v>0</v>
+      </c>
+      <c r="V8">
+        <v>0</v>
+      </c>
+      <c r="W8">
         <v>0.1072083333333333</v>
       </c>
-      <c r="X3">
-        <v>0.1145958189441398</v>
-      </c>
-      <c r="Y3">
-        <v>-0.007387485610806446</v>
-      </c>
-      <c r="Z3">
+      <c r="X8">
+        <v>0.114561836946367</v>
+      </c>
+      <c r="Y8">
+        <v>-0.007353503613033621</v>
+      </c>
+      <c r="Z8">
         <v>1.414904296613573</v>
       </c>
-      <c r="AA3">
+      <c r="AA8">
         <v>0.1010520392882865</v>
       </c>
-      <c r="AB3">
-        <v>0.07305128397350807</v>
-      </c>
-      <c r="AC3">
-        <v>0.0280007553147784</v>
-      </c>
-      <c r="AD3">
+      <c r="AB8">
+        <v>0.07303741143649339</v>
+      </c>
+      <c r="AC8">
+        <v>0.02801462785179308</v>
+      </c>
+      <c r="AD8">
         <v>457.2</v>
       </c>
-      <c r="AE3">
-        <v>0</v>
-      </c>
-      <c r="AF3">
+      <c r="AE8">
+        <v>0</v>
+      </c>
+      <c r="AF8">
         <v>457.2</v>
       </c>
-      <c r="AG3">
+      <c r="AG8">
         <v>457.2</v>
       </c>
-      <c r="AH3">
+      <c r="AH8">
         <v>0.591768055915092</v>
       </c>
-      <c r="AI3">
+      <c r="AI8">
         <v>0.1686711429203866</v>
       </c>
-      <c r="AJ3">
+      <c r="AJ8">
         <v>0.591768055915092</v>
       </c>
-      <c r="AK3">
+      <c r="AK8">
         <v>0.1686711429203866</v>
       </c>
-      <c r="AL3">
+      <c r="AL8">
         <v>15.3</v>
       </c>
-      <c r="AM3">
+      <c r="AM8">
         <v>15.3</v>
       </c>
-      <c r="AN3">
+      <c r="AN8">
         <v>0.8978790259230165</v>
       </c>
-      <c r="AO3">
+      <c r="AO8">
         <v>28.75816993464052</v>
       </c>
-      <c r="AP3">
+      <c r="AP8">
         <v>0.8978790259230165</v>
       </c>
-      <c r="AQ3">
+      <c r="AQ8">
         <v>28.75816993464052</v>
       </c>
     </row>
